--- a/assets/work/Jill Jones initial overview.xlsx
+++ b/assets/work/Jill Jones initial overview.xlsx
@@ -9,11 +9,10 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="formats" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <si>
     <t>*Date of birth 30. Jun, 1989</t>
   </si>
@@ -134,6 +133,408 @@
   </si>
   <si>
     <t>Jill Jones</t>
+  </si>
+  <si>
+    <t>Date of birth: 15. Jan, 1994</t>
+  </si>
+  <si>
+    <t>Daily Sick Pay (for a 80.000 € income)</t>
+  </si>
+  <si>
+    <t>Basics</t>
+  </si>
+  <si>
+    <t>Amount of deductible</t>
+  </si>
+  <si>
+    <t>No-claim bonus refund</t>
+  </si>
+  <si>
+    <t>Hospital Stay</t>
+  </si>
+  <si>
+    <t>Status and comfort</t>
+  </si>
+  <si>
+    <t>Medical treatments</t>
+  </si>
+  <si>
+    <t>Accommodation</t>
+  </si>
+  <si>
+    <t>Outpatient</t>
+  </si>
+  <si>
+    <t>Doctors and medical specialists</t>
+  </si>
+  <si>
+    <t>Prescribed medication</t>
+  </si>
+  <si>
+    <t>Vision aids</t>
+  </si>
+  <si>
+    <t>Laser eye surgery</t>
+  </si>
+  <si>
+    <t>Prescribed physical therapy</t>
+  </si>
+  <si>
+    <t>Medical devices (wheelchairs, etc.)</t>
+  </si>
+  <si>
+    <t>Test-tube fertilization</t>
+  </si>
+  <si>
+    <t>Vaccinations</t>
+  </si>
+  <si>
+    <t>Psychotherapy (with approval)</t>
+  </si>
+  <si>
+    <t>Extras</t>
+  </si>
+  <si>
+    <t>Natural &amp; alternative medicine</t>
+  </si>
+  <si>
+    <t>Childbirth</t>
+  </si>
+  <si>
+    <t>Dental</t>
+  </si>
+  <si>
+    <t>Dental treatment and prophylaxis</t>
+  </si>
+  <si>
+    <t>Inlays</t>
+  </si>
+  <si>
+    <t>Crowns and dentures</t>
+  </si>
+  <si>
+    <t>Implants</t>
+  </si>
+  <si>
+    <t>Orthodontics</t>
+  </si>
+  <si>
+    <t>Prosthetics (cost estimates)</t>
+  </si>
+  <si>
+    <t>Dental work (cost limits)</t>
+  </si>
+  <si>
+    <t>Helpful extra tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prices subject to increase in January each year. </t>
+  </si>
+  <si>
+    <t>For expats only.</t>
+  </si>
+  <si>
+    <t>Inter / LA-VNS U</t>
+  </si>
+  <si>
+    <t>Ref 189/356</t>
+  </si>
+  <si>
+    <t>186,89 € + 9,34 €</t>
+  </si>
+  <si>
+    <t>64,17 €</t>
+  </si>
+  <si>
+    <t>79,39 €</t>
+  </si>
+  <si>
+    <t>170 €/day as of 43rd day</t>
+  </si>
+  <si>
+    <t>Melvin's monthly cost (age 8)</t>
+  </si>
+  <si>
+    <t>148,83 €</t>
+  </si>
+  <si>
+    <t>339,79 €</t>
+  </si>
+  <si>
+    <t>318,73 €</t>
+  </si>
+  <si>
+    <t>300 €/year</t>
+  </si>
+  <si>
+    <t>No refund is available</t>
+  </si>
+  <si>
+    <t>Private patient - more comfort</t>
+  </si>
+  <si>
+    <t>Head physician</t>
+  </si>
+  <si>
+    <t>Single room</t>
+  </si>
+  <si>
+    <t>100%, with direct access to specialists</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>Up to 250 €, every 2 years</t>
+  </si>
+  <si>
+    <t>No reimbursement</t>
+  </si>
+  <si>
+    <t>100% of catalogue</t>
+  </si>
+  <si>
+    <t>Not insured</t>
+  </si>
+  <si>
+    <t>100% statutory standard (excl. travel shots)</t>
+  </si>
+  <si>
+    <t>100% up to 20 sessions/year</t>
+  </si>
+  <si>
+    <t>Standard benefits - no extras</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>Submission of a cost plan is obligatory</t>
+  </si>
+  <si>
+    <t>Cap at 2.500 €/year</t>
+  </si>
+  <si>
+    <t>Special rate for expats who will be temporarily in Germany</t>
+  </si>
+  <si>
+    <t>Straightforward application - no medical assessment needed</t>
+  </si>
+  <si>
+    <t>Upgrade into long-term plan with INTER upon medical assessment possible</t>
+  </si>
+  <si>
+    <t>Gothaer / MediVita250</t>
+  </si>
+  <si>
+    <t>Ref 125/1155</t>
+  </si>
+  <si>
+    <t>577,75 € + 35,47 €</t>
+  </si>
+  <si>
+    <t>71,40 €</t>
+  </si>
+  <si>
+    <t>Melvin's monthly cost (age 7)</t>
+  </si>
+  <si>
+    <t>191,66 €</t>
+  </si>
+  <si>
+    <t>748,79 €</t>
+  </si>
+  <si>
+    <t>566,06 €</t>
+  </si>
+  <si>
+    <t>250 €/year</t>
+  </si>
+  <si>
+    <t>Refund of 1.520 € / year possible</t>
+  </si>
+  <si>
+    <t>No privileges</t>
+  </si>
+  <si>
+    <t>Ward physician</t>
+  </si>
+  <si>
+    <t>Shared room</t>
+  </si>
+  <si>
+    <t>Up to 100 €, every year</t>
+  </si>
+  <si>
+    <t>100%, prior approval needed</t>
+  </si>
+  <si>
+    <t>80% up to 20 sessions/year</t>
+  </si>
+  <si>
+    <t>100%, up to 2.000 €/year</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Medium good value plan</t>
+  </si>
+  <si>
+    <t>Dental claims don't jeopardize the no-claims bonus</t>
+  </si>
+  <si>
+    <t>Flexible adaptable</t>
+  </si>
+  <si>
+    <t>BBKK / GesundheitVARIO 800</t>
+  </si>
+  <si>
+    <t>Ref 3814/1138</t>
+  </si>
+  <si>
+    <t>601,23 € + 50,00 €</t>
+  </si>
+  <si>
+    <t>63,04 €</t>
+  </si>
+  <si>
+    <t>57,80 €</t>
+  </si>
+  <si>
+    <t>295,70 €</t>
+  </si>
+  <si>
+    <t>772,07 €</t>
+  </si>
+  <si>
+    <t>681,74 €</t>
+  </si>
+  <si>
+    <t>800 €/year</t>
+  </si>
+  <si>
+    <t>Refund of 800 € / year possible</t>
+  </si>
+  <si>
+    <t>100%, incl. contraception pill</t>
+  </si>
+  <si>
+    <t>Up to 500 €, every 2 years</t>
+  </si>
+  <si>
+    <t>100% incl. travel shots</t>
+  </si>
+  <si>
+    <t>Waiver of contribution up to 6 months (when entitled to parental allowance)</t>
+  </si>
+  <si>
+    <t>70%</t>
+  </si>
+  <si>
+    <t>100%, for kids/teens only</t>
+  </si>
+  <si>
+    <t>Cost plan not mandatory, but advised</t>
+  </si>
+  <si>
+    <t>Cost limits in the first 3 years</t>
+  </si>
+  <si>
+    <t>Fulfils the highest demands</t>
+  </si>
+  <si>
+    <t>Generous upgrading and downgrading options</t>
+  </si>
+  <si>
+    <t>Worldwide coverage up to 12 months/trip</t>
+  </si>
+  <si>
+    <t>SHI / KV</t>
+  </si>
+  <si>
+    <t>Ref 3641/321</t>
+  </si>
+  <si>
+    <t>1.004,98 € + 55,00 €</t>
+  </si>
+  <si>
+    <t>244,13 €</t>
+  </si>
+  <si>
+    <t>0,00 €</t>
+  </si>
+  <si>
+    <t>Not selected</t>
+  </si>
+  <si>
+    <t>205,35 €</t>
+  </si>
+  <si>
+    <t>1.304,11 €</t>
+  </si>
+  <si>
+    <t>857,41 €</t>
+  </si>
+  <si>
+    <t>0 €/year</t>
+  </si>
+  <si>
+    <t>100%, but not private doctors and often long waiting times</t>
+  </si>
+  <si>
+    <t>10% co-pay (not more than 10 €/drug)</t>
+  </si>
+  <si>
+    <t>only for children or if there is a severe visual impairment</t>
+  </si>
+  <si>
+    <t>10% co-pay plus 10 € co-pay per prescription</t>
+  </si>
+  <si>
+    <t>10% co-pay (not more than 10 €/device)</t>
+  </si>
+  <si>
+    <t>50%, prior approval needed</t>
+  </si>
+  <si>
+    <t>100% according to StiKo (excl. travel shots)</t>
+  </si>
+  <si>
+    <t>100% (but often long waiting times)</t>
+  </si>
+  <si>
+    <t>usually not covered</t>
+  </si>
+  <si>
+    <t>Standard benefits</t>
+  </si>
+  <si>
+    <t>Basic treatments covered, dental cleaning usually not covered</t>
+  </si>
+  <si>
+    <t>not covered</t>
+  </si>
+  <si>
+    <t>Simple standard only</t>
+  </si>
+  <si>
+    <t>not included, only very small subsidy</t>
+  </si>
+  <si>
+    <t>100% for kids/teen only</t>
+  </si>
+  <si>
+    <t>No cap for dental expenses, but overall the subsidy is limited to simple standard solutions</t>
+  </si>
+  <si>
+    <t>Invidividual customization is not possible</t>
+  </si>
+  <si>
+    <t>The benefits are subject to budget restrictions imposed by the state</t>
+  </si>
+  <si>
+    <t>Dependents can be included cost-free</t>
   </si>
 </sst>
 </file>
@@ -550,7 +951,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -559,7 +960,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="184731" cy="264560"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="Textfeld 5">
           <a:extLst>
@@ -606,6 +1007,191 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2038350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+        <a:ln/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2228850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+        <a:ln/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2667000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+        <a:ln/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1714500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+        <a:ln/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2114550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 7" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="false"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+        <a:ln/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="true" fPrintsWithSheet="true"/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -885,8 +1471,6 @@
     <col customWidth="true" max="8" min="8" width="39.7109375"/>
     <col customWidth="true" max="9" min="9" width="1.7109375"/>
     <col customWidth="true" max="10" min="10" width="39.7109375"/>
-    <col customWidth="true" max="11" min="11" width="1.7109375"/>
-    <col customWidth="true" max="12" min="12" width="39.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="true" ht="90" customHeight="true">
@@ -894,213 +1478,654 @@
       <c r="F1" s="2"/>
       <c r="H1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12" s="1" customFormat="true" ht="60" customHeight="true"/>
     <row r="3" spans="1:12" s="1" customFormat="true" ht="23.25">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="D3" s="33" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="true" ht="18.75">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="5" spans="1:12" s="31" customFormat="true" ht="12.75">
       <c r="A5" s="30"/>
+      <c r="D5" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="6" spans="1:12" s="1" customFormat="true">
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="7" spans="1:12" s="1" customFormat="true">
       <c r="A7" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="D7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="8" spans="1:12" s="1" customFormat="true">
       <c r="A8" s="35" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B8" s="35"/>
-      <c r="D8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="L8" s="29"/>
+      <c r="D8" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="9" spans="1:12" s="1" customFormat="true">
       <c r="A9" s="35"/>
       <c r="B9" s="35"/>
-      <c r="D9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="D9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="true"/>
     <row r="11" spans="1:12" s="1" customFormat="true">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="L11" s="11"/>
-    </row>
-    <row r="12" spans="1:12" s="1" customFormat="true">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="L12" s="11"/>
-    </row>
-    <row r="13" spans="1:12" s="1" customFormat="true">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="L13" s="11"/>
-    </row>
-    <row r="14" spans="1:12" s="1" customFormat="true">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="L14" s="11"/>
-    </row>
+      <c r="A11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="1" customFormat="true" ht="18.75">
+      <c r="A12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="1" customFormat="true" ht="23.25">
+      <c r="A13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="1" customFormat="true"/>
     <row r="15" spans="1:12" s="1" customFormat="true">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="L15" s="11"/>
+      <c r="A15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="16" spans="1:12" s="1" customFormat="true">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="L16" s="11"/>
-    </row>
-    <row r="17" spans="1:12" s="1" customFormat="true">
-      <c r="A17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="L17" s="11"/>
-    </row>
+      <c r="A16" s="12"/>
+      <c r="B16" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="1" customFormat="true"/>
     <row r="18" spans="1:12" s="1" customFormat="true">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="L18" s="11"/>
+      <c r="A18" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="19" spans="1:12" s="1" customFormat="true">
-      <c r="A19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="L19" s="11"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="20" spans="1:12" s="1" customFormat="true">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="L20" s="11"/>
-    </row>
-    <row r="21" spans="1:12" s="1" customFormat="true" ht="18.75">
-      <c r="A21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:12" s="1" customFormat="true" ht="23.25">
-      <c r="A22" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:12" s="1" customFormat="true"/>
-    <row r="24" spans="1:12" s="1" customFormat="true"/>
-    <row r="25" spans="1:12" s="1" customFormat="true"/>
-    <row r="26" spans="1:12" s="1" customFormat="true"/>
-    <row r="27" spans="1:12" s="1" customFormat="true"/>
-    <row r="28" spans="1:12" s="1" customFormat="true"/>
-    <row r="29" spans="1:12" s="1" customFormat="true"/>
-    <row r="30" spans="1:12" s="1" customFormat="true"/>
-    <row r="31" spans="1:12" s="1" customFormat="true"/>
-    <row r="32" spans="1:12" s="1" customFormat="true"/>
-    <row r="33" s="1" customFormat="true"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="1" customFormat="true"/>
+    <row r="22" spans="1:12" s="1" customFormat="true">
+      <c r="A22" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="1" customFormat="true">
+      <c r="A23" s="18"/>
+      <c r="B23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="true">
+      <c r="A24" s="18"/>
+      <c r="B24" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="true">
+      <c r="A25" s="18"/>
+      <c r="B25" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="true">
+      <c r="A26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="true">
+      <c r="A27" s="18"/>
+      <c r="B27" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="true">
+      <c r="A28" s="18"/>
+      <c r="B28" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="true">
+      <c r="A29" s="18"/>
+      <c r="B29" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="true">
+      <c r="A30" s="18"/>
+      <c r="B30" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="true"/>
+    <row r="32" s="1" customFormat="true">
+      <c r="A32" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="J32" s="23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="true">
+      <c r="A33" s="21"/>
+      <c r="B33" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="J33" s="23" t="s">
+        <v>156</v>
+      </c>
+    </row>
     <row r="34" s="1" customFormat="true"/>
-    <row r="35" s="1" customFormat="true"/>
-    <row r="36" s="1" customFormat="true"/>
-    <row r="37" s="1" customFormat="true"/>
-    <row r="38" s="1" customFormat="true"/>
-    <row r="39" s="1" customFormat="true"/>
-    <row r="40" s="1" customFormat="true"/>
-    <row r="41" s="1" customFormat="true"/>
+    <row r="35" s="1" customFormat="true">
+      <c r="A35" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H35" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J35" s="26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="true">
+      <c r="A36" s="24"/>
+      <c r="B36" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H36" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J36" s="26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="true">
+      <c r="A37" s="24"/>
+      <c r="B37" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H37" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="J37" s="26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="true">
+      <c r="A38" s="24"/>
+      <c r="B38" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="J38" s="26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="true">
+      <c r="A39" s="24"/>
+      <c r="B39" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H39" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="J39" s="26" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="true">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="F40" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H40" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="J40" s="26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="true">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H41" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="J41" s="26" t="s">
+        <v>162</v>
+      </c>
+    </row>
     <row r="42" s="1" customFormat="true"/>
-    <row r="43" s="1" customFormat="true"/>
-    <row r="44" s="1" customFormat="true"/>
-    <row r="45" s="1" customFormat="true"/>
+    <row r="43" s="1" customFormat="true">
+      <c r="A43" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="D43" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="H43" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="J43" s="27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="true">
+      <c r="A44" s="28"/>
+      <c r="B44" s="28"/>
+      <c r="D44" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="H44" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="J44" s="27" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="true">
+      <c r="A45" s="28"/>
+      <c r="B45" s="28"/>
+      <c r="D45" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="H45" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="J45" s="27" t="s">
+        <v>165</v>
+      </c>
+    </row>
     <row r="46" s="1" customFormat="true"/>
-    <row r="47" s="1" customFormat="true"/>
+    <row r="47" s="1" customFormat="true">
+      <c r="A47" s="36" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="48" s="1" customFormat="true"/>
     <row r="49" s="1" customFormat="true"/>
     <row r="50" s="1" customFormat="true"/>
@@ -1400,165 +2425,18 @@
     <row r="344" s="1" customFormat="true"/>
     <row r="345" s="1" customFormat="true"/>
     <row r="346" s="1" customFormat="true"/>
-    <row r="347" s="1" customFormat="true"/>
-    <row r="348" s="1" customFormat="true"/>
-    <row r="349" s="1" customFormat="true"/>
-    <row r="350" s="1" customFormat="true"/>
-    <row r="351" s="1" customFormat="true"/>
-    <row r="352" s="1" customFormat="true"/>
-    <row r="353" s="1" customFormat="true"/>
-    <row r="354" s="1" customFormat="true"/>
-    <row r="355" s="1" customFormat="true"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="7">
     <mergeCell ref="A8:B9"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A35:A41"/>
+    <mergeCell ref="A43:B45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup horizontalDpi="4294967293" r:id="rId1" orientation="portrait"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:E21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="22.28515625"/>
-    <col customWidth="true" max="5" min="5" width="22.42578125"/>
-  </cols>
-  <sheetData>
-    <row r="1"/>
-    <row r="2" spans="2:5" ht="23.25">
-      <c r="B2" s="34" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" spans="2:5" ht="18.75">
-      <c r="B4" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="18.75">
-      <c r="B5" s="15"/>
-      <c r="C5" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="2:5" ht="37.5">
-      <c r="B7" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="2:5" ht="37.5">
-      <c r="B9" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="2:5" ht="18.75">
-      <c r="B11" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="2:5" ht="18.75">
-      <c r="B13" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15" spans="2:5" ht="18.75">
-      <c r="B15" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17" spans="2:2">
-      <c r="B17" s="32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19" spans="2:2">
-      <c r="B19" s="33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21" spans="2:2">
-      <c r="B21" s="36" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup horizontalDpi="4294967293" r:id="rId1" orientation="portrait"/>
-</worksheet>
 </file>
--- a/assets/work/Jill Jones initial overview.xlsx
+++ b/assets/work/Jill Jones initial overview.xlsx
@@ -12,7 +12,8 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Quote" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
   <si>
     <t>*Date of birth 30. Jun, 1989</t>
   </si>
@@ -536,12 +537,171 @@
   <si>
     <t>Dependents can be included cost-free</t>
   </si>
+  <si>
+    <t>Quote Summary</t>
+  </si>
+  <si>
+    <t>Client name</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>Birth date</t>
+  </si>
+  <si>
+    <t>1994-01-15</t>
+  </si>
+  <si>
+    <t>Buy date</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>Sick cover</t>
+  </si>
+  <si>
+    <t>80.000 €</t>
+  </si>
+  <si>
+    <t>Prior cover</t>
+  </si>
+  <si>
+    <t>No prior cover</t>
+  </si>
+  <si>
+    <t>Exam</t>
+  </si>
+  <si>
+    <t>Exam OK</t>
+  </si>
+  <si>
+    <t>Specialist</t>
+  </si>
+  <si>
+    <t>Not important</t>
+  </si>
+  <si>
+    <t>Vision</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Temp visa</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>No PVN</t>
+  </si>
+  <si>
+    <t>Natural medicine</t>
+  </si>
+  <si>
+    <t>Plan 1</t>
+  </si>
+  <si>
+    <t>Pre-ex total</t>
+  </si>
+  <si>
+    <t>9,34 €</t>
+  </si>
+  <si>
+    <t>Vision correction</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Selected addon</t>
+  </si>
+  <si>
+    <t>Pre-ex</t>
+  </si>
+  <si>
+    <t>Optional note</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Sick</t>
+  </si>
+  <si>
+    <t>43A</t>
+  </si>
+  <si>
+    <t>PVN</t>
+  </si>
+  <si>
+    <t>Plan 2</t>
+  </si>
+  <si>
+    <t>Age mode</t>
+  </si>
+  <si>
+    <t>Exact-age</t>
+  </si>
+  <si>
+    <t>35,47 €</t>
+  </si>
+  <si>
+    <t>5,00 €</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Consumer</t>
+  </si>
+  <si>
+    <t>Natural</t>
+  </si>
+  <si>
+    <t>Plan 3</t>
+  </si>
+  <si>
+    <t>50,00 €</t>
+  </si>
+  <si>
+    <t>Plan 4</t>
+  </si>
+  <si>
+    <t>55,00 €</t>
+  </si>
+  <si>
+    <t>Dependants</t>
+  </si>
+  <si>
+    <t>Dependant</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Melvin</t>
+  </si>
+  <si>
+    <t>2018-07-01</t>
+  </si>
+  <si>
+    <t>Pre-ex charges</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -671,8 +831,19 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -711,6 +882,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEEEE"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -827,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment wrapText="true"/>
@@ -927,6 +1103,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2439,4 +2627,633 @@
   <pageSetup horizontalDpi="4294967293" r:id="rId1" orientation="portrait"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="34"/>
+    <col customWidth="true" max="2" min="2" width="40"/>
+    <col customWidth="true" max="3" min="3" width="16"/>
+    <col customWidth="true" max="4" min="4" width="42"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="39"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="B37" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="C37" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="B41" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="39"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="C43" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="D43" s="40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B46" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="B47" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C47" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C48" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B49" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C49" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="B51" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="39"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="B55" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="B56" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="C57" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="D57" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="38" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="38" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="B62" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="B63" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="B65" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>